--- a/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (9)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (15)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBEB289-771C-41E1-9A45-8A5B9EC05BF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6297BC-C6DF-48FF-BAD8-A47A4BD07725}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>图片个数</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>是否粘贴二维码</t>
   </si>
@@ -369,27 +366,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="35.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="46.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (15)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (17)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6297BC-C6DF-48FF-BAD8-A47A4BD07725}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2D6393-D9C7-4FDA-8717-EE313852EEE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,13 +27,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>是否粘贴二维码</t>
-  </si>
-  <si>
     <t>SystemID/厂商报修ID</t>
   </si>
   <si>
     <t>代理商</t>
+  </si>
+  <si>
+    <t>二维码是否已实施(粘贴及照片上传)</t>
   </si>
 </sst>
 </file>
@@ -376,13 +376,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (17)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (20)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2D6393-D9C7-4FDA-8717-EE313852EEE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8471EE8D-C189-46D3-AB42-23F76D4F0404}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>SystemID/厂商报修ID</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>二维码是否已实施(粘贴及照片上传)</t>
+  </si>
+  <si>
+    <t>合同编号</t>
   </si>
 </sst>
 </file>
@@ -366,15 +369,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.21875" style="2" customWidth="1"/>
+    <col min="2" max="3" width="35.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="46.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -382,6 +385,9 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/assetStatistic/Asset_Statistic_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (20)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (4)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8471EE8D-C189-46D3-AB42-23F76D4F0404}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC183DC-BF27-42E3-A8BF-D9E4E2F47EA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>SystemID/厂商报修ID</t>
   </si>
@@ -37,6 +37,18 @@
   </si>
   <si>
     <t>合同编号</t>
+  </si>
+  <si>
+    <t>医院名称</t>
+  </si>
+  <si>
+    <t>设备型号</t>
+  </si>
+  <si>
+    <t>是否设备无法粘贴二维码</t>
+  </si>
+  <si>
+    <t>无法粘贴二维码原因</t>
   </si>
 </sst>
 </file>
@@ -369,26 +381,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="35.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="46.21875" style="2" customWidth="1"/>
+    <col min="1" max="3" width="36.77734375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="35.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
